--- a/public/contoh_excel/TEMPLATE INPUT TAGIHAN.xlsx
+++ b/public/contoh_excel/TEMPLATE INPUT TAGIHAN.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Tagihan" sheetId="1" r:id="rId4"/>
+    <sheet name="Data Siswa" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -15,36 +15,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
   <si>
     <t>NIS</t>
   </si>
   <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>KELAS</t>
+  </si>
+  <si>
+    <t>KELOMPOK</t>
+  </si>
+  <si>
+    <t>ANGKATAN</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t>ALAMAT</t>
+  </si>
+  <si>
+    <t>ORTU</t>
+  </si>
+  <si>
     <t>NOMINAL</t>
   </si>
   <si>
-    <t>NAMA_TAGIHAN</t>
-  </si>
-  <si>
-    <t>PERIODE</t>
-  </si>
-  <si>
-    <t>TAHUN_AKADEMIK</t>
-  </si>
-  <si>
-    <t>CICIL</t>
-  </si>
-  <si>
-    <t>1234567801</t>
-  </si>
-  <si>
-    <t>BULAN SEPTEMBER</t>
-  </si>
-  <si>
-    <t>202609</t>
+    <t>FULAN 1</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
   <si>
     <t>2026/2027</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Semarang</t>
+  </si>
+  <si>
+    <t>Gatot</t>
   </si>
 </sst>
 </file>
@@ -72,12 +93,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -92,9 +119,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,18 +432,22 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="10.426" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="11.569" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -424,25 +466,49 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>300000</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2">
+    <row r="2" spans="1:10">
+      <c r="A2" s="2">
+        <v>770078</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2">
         <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="4">
+        <v>500000</v>
       </c>
     </row>
   </sheetData>
